--- a/base_datas/media_nacional_detalhamento.xlsx
+++ b/base_datas/media_nacional_detalhamento.xlsx
@@ -593,49 +593,49 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>657.906128935444</v>
+        <v>658.3641763765232</v>
       </c>
       <c r="B2">
-        <v>173.8196139099241</v>
+        <v>171.3686857275708</v>
       </c>
       <c r="C2">
-        <v>6832.743459847115</v>
+        <v>6837.431603471166</v>
       </c>
       <c r="D2">
-        <v>389.7008261691104</v>
+        <v>382.4792999844857</v>
       </c>
       <c r="E2">
-        <v>601.9841628377819</v>
+        <v>602.297418541935</v>
       </c>
       <c r="F2">
-        <v>54.20861562466339</v>
+        <v>54.24777148477003</v>
       </c>
       <c r="G2">
-        <v>16.50236859554457</v>
+        <v>16.490101028973</v>
       </c>
       <c r="H2">
-        <v>240.2296292986271</v>
+        <v>240.3530040301063</v>
       </c>
       <c r="I2">
-        <v>66.67048953546843</v>
+        <v>66.70530457058322</v>
       </c>
       <c r="J2">
-        <v>12.66563767793719</v>
+        <v>3.775339221653982</v>
       </c>
       <c r="K2">
-        <v>4068.926955982995</v>
+        <v>4071.369555462616</v>
       </c>
       <c r="L2">
-        <v>1779.353406748903</v>
+        <v>1781.036501306445</v>
       </c>
       <c r="M2">
-        <v>986.2508451516062</v>
+        <v>986.8164223867379</v>
       </c>
       <c r="N2">
-        <v>237.5044061729009</v>
+        <v>231.8058618275529</v>
       </c>
       <c r="O2">
-        <v>128.0527979006407</v>
+        <v>125.3132016539095</v>
       </c>
       <c r="P2">
         <v>8.765542271102587</v>
@@ -644,19 +644,19 @@
         <v>10.61667910088558</v>
       </c>
       <c r="R2">
-        <v>76.32910555035717</v>
+        <v>76.34824310554924</v>
       </c>
       <c r="S2">
-        <v>78.11405439717291</v>
+        <v>78.15561281465889</v>
       </c>
       <c r="T2">
-        <v>82.62388821800103</v>
+        <v>82.65037883792331</v>
       </c>
       <c r="U2">
-        <v>251.6656890497605</v>
+        <v>251.8395609858809</v>
       </c>
       <c r="V2">
-        <v>190.2196539031093</v>
+        <v>190.279074586054</v>
       </c>
       <c r="W2">
         <v>3928.699041553994</v>
@@ -665,16 +665,16 @@
         <v>619.6702869300105</v>
       </c>
       <c r="Y2">
-        <v>5.315492108569766</v>
+        <v>5.322152224965593</v>
       </c>
       <c r="Z2">
-        <v>24.73324089545927</v>
+        <v>24.74707051074736</v>
       </c>
       <c r="AA2">
-        <v>36.13219371644946</v>
+        <v>36.16206635983463</v>
       </c>
       <c r="AB2">
-        <v>2.845496509466277E-16</v>
+        <v>2.847835029342036E-16</v>
       </c>
       <c r="AC2">
         <v>9.39919425056576</v>
@@ -686,49 +686,49 @@
         <v>35.54273628572435</v>
       </c>
       <c r="AF2">
-        <v>7.277793482567173</v>
+        <v>7.203632527997629</v>
       </c>
       <c r="AG2">
-        <v>2717.390378325714</v>
+        <v>2719.993551176361</v>
       </c>
       <c r="AH2">
         <v>429.4473048975834</v>
       </c>
       <c r="AI2">
-        <v>193.2533378638279</v>
+        <v>193.2604058899925</v>
       </c>
       <c r="AJ2">
-        <v>588.8558996320795</v>
+        <v>589.335231463309</v>
       </c>
       <c r="AK2">
-        <v>120.9052166859761</v>
+        <v>121.0084888452842</v>
       </c>
       <c r="AL2">
-        <v>407.8467957606125</v>
+        <v>408.1502648707133</v>
       </c>
       <c r="AM2">
-        <v>40.79999927054286</v>
+        <v>40.82413602364235</v>
       </c>
       <c r="AN2">
-        <v>159.8449036961663</v>
+        <v>158.7970447404655</v>
       </c>
       <c r="AO2">
-        <v>1377.955076962981</v>
+        <v>1378.815825784344</v>
       </c>
       <c r="AP2">
-        <v>144.2395690427456</v>
+        <v>144.3358468842603</v>
       </c>
       <c r="AQ2">
-        <v>110.1226931333414</v>
+        <v>110.1765617319684</v>
       </c>
       <c r="AR2">
-        <v>13.20452041699421</v>
+        <v>13.21024987666506</v>
       </c>
       <c r="AS2">
-        <v>36.29005091324641</v>
+        <v>36.26102709956321</v>
       </c>
       <c r="AT2">
-        <v>158.0198538746868</v>
+        <v>158.1388563519337</v>
       </c>
       <c r="AU2">
         <v>1</v>
